--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T09:58:03+00:00</t>
+    <t>2026-01-26T12:56:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T12:56:49+00:00</t>
+    <t>2026-02-05T13:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Encounter|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Encounter</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -504,7 +504,7 @@
     <t>TDDUIAdmissionDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-admission-date|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-admission-date}
 </t>
   </si>
   <si>
@@ -523,7 +523,7 @@
     <t>TDDUIEntryModelabel</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-entry-mode-label|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-entry-mode-label}
 </t>
   </si>
   <si>
@@ -542,7 +542,7 @@
     <t>TDDUIExitModeLabel</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-exit-mode-label|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-exit-mode-label}
 </t>
   </si>
   <si>
@@ -561,7 +561,7 @@
     <t>TDDUIComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-comment|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-comment}
 </t>
   </si>
   <si>
@@ -746,7 +746,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-identifier-vs|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-identifier-vs</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -968,7 +968,7 @@
     <t>Classification of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -1073,7 +1073,7 @@
     <t>Indicates the urgency of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
   </si>
   <si>
     <t>.priorityCode</t>
@@ -1092,7 +1092,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins)
 </t>
   </si>
   <si>
@@ -1614,7 +1614,7 @@
     <t>The reason for re-admission of this hospitalization encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092|2.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
   </si>
   <si>
     <t>PV1-13</t>
@@ -1823,7 +1823,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
 </t>
   </si>
   <si>
@@ -2178,7 +2178,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="150.68359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="131.66796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2193,7 +2193,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="64.00390625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.91015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.40234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T13:38:35+00:00</t>
+    <t>2026-02-05T14:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T14:50:20+00:00</t>
+    <t>2026-02-05T15:15:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -739,14 +739,14 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-encounter-identifier-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-encounter-identifier"/&gt;
     &lt;code value="SEJ"/&gt;
     &lt;display value="Identifiant du séjour"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-identifier-vs</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-identifier</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -2193,7 +2193,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="64.00390625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.40234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.0859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T15:15:02+00:00</t>
+    <t>2026-02-06T13:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T13:40:54+00:00</t>
+    <t>2026-02-06T14:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-19T15:19:47+00:00</t>
+    <t>2026-02-25T14:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T14:12:38+00:00</t>
+    <t>2026-02-26T10:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3450" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4038" uniqueCount="642">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T10:50:19+00:00</t>
+    <t>2026-02-26T16:06:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -868,6 +868,51 @@
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
+    <t>Encounter.identifier:AdministrativeFileNumber</t>
+  </si>
+  <si>
+    <t>AdministrativeFileNumber</t>
+  </si>
+  <si>
+    <t>Numéro de dossier administratif du séjour</t>
+  </si>
+  <si>
+    <t>numeroDossierAdministratifSejour</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.id</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.extension</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.use</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.type</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-encounter-identifier"/&gt;
+    &lt;code value="NUMDOSS"/&gt;
+    &lt;display value="Numéro de dossier administratif du séjour"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.system</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.value</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.period</t>
+  </si>
+  <si>
+    <t>Encounter.identifier:AdministrativeFileNumber.assigner</t>
+  </si>
+  <si>
     <t>Encounter.status</t>
   </si>
   <si>
@@ -1055,10 +1100,10 @@
     <t>Broad categorization of the service that is to be provided (e.g. cardiology).</t>
   </si>
   <si>
-    <t>Broad categorization of the service that is to be provided.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J226-ModaliteAccueil-ROR/FHIR/JDV-J226-ModaliteAccueil-ROR</t>
+  </si>
+  <si>
+    <t>modaliteAccueil</t>
   </si>
   <si>
     <t>PV1-10</t>
@@ -1254,6 +1299,92 @@
   </si>
   <si>
     <t>ROL-4</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
+    <t>origineDemande</t>
   </si>
   <si>
     <t>Encounter.appointment</t>
@@ -1550,6 +1681,25 @@
     <t>Encounter.hospitalization.extension</t>
   </si>
   <si>
+    <t>Encounter.hospitalization.extension:TDDUIEntryDateOrigin</t>
+  </si>
+  <si>
+    <t>TDDUIEntryDateOrigin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-entry-date-origin}
+</t>
+  </si>
+  <si>
+    <t>TDDUI Entry Date Origin</t>
+  </si>
+  <si>
+    <t>Extension permettant de véhiculer la date d'entrée dans l'ESSMS de provenance.</t>
+  </si>
+  <si>
+    <t>dateEntreeESSMSProvenance</t>
+  </si>
+  <si>
     <t>Encounter.hospitalization.modifierExtension</t>
   </si>
   <si>
@@ -1562,136 +1712,146 @@
     <t>Pre-admission identifier.</t>
   </si>
   <si>
+    <t>numeroDossierESSMSProvenance</t>
+  </si>
+  <si>
     <t>PV1-5</t>
   </si>
   <si>
     <t>Encounter.hospitalization.origin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
+</t>
+  </si>
+  <si>
+    <t>The location/organization from which the patient came before admission</t>
+  </si>
+  <si>
+    <t>The location/organization from which the patient came before admission.</t>
+  </si>
+  <si>
+    <t>ESSMSProvenance</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=ORG].role</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.admitSource</t>
+  </si>
+  <si>
+    <t>From where patient was admitted (physician referral, transfer)</t>
+  </si>
+  <si>
+    <t>From where patient was admitted (physician referral, transfer).</t>
+  </si>
+  <si>
+    <t>From where the patient was admitted.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
+  </si>
+  <si>
+    <t>.admissionReferralSourceCode</t>
+  </si>
+  <si>
+    <t>PV1-14</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.reAdmission</t>
+  </si>
+  <si>
+    <t>The type of hospital re-admission that has occurred (if any). If the value is absent, then this is not identified as a readmission</t>
+  </si>
+  <si>
+    <t>Whether this hospitalization is a readmission and why if known.</t>
+  </si>
+  <si>
+    <t>The reason for re-admission of this hospitalization encounter.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
+  </si>
+  <si>
+    <t>PV1-13</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dietPreference</t>
+  </si>
+  <si>
+    <t>Diet preferences reported by the patient</t>
+  </si>
+  <si>
+    <t>Diet preferences reported by the patient.</t>
+  </si>
+  <si>
+    <t>For example, a patient may request both a dairy-free and nut-free diet preference (not mutually exclusive).</t>
+  </si>
+  <si>
+    <t>Used to track patient's diet restrictions and/or preference. For a complete description of the nutrition needs of a patient during their stay, one should use the nutritionOrder resource which links to Encounter.</t>
+  </si>
+  <si>
+    <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
+  </si>
+  <si>
+    <t>PV1-38</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialCourtesy</t>
+  </si>
+  <si>
+    <t>Special courtesies (VIP, board member)</t>
+  </si>
+  <si>
+    <t>Special courtesies (VIP, board member).</t>
+  </si>
+  <si>
+    <t>Special courtesies.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
+  </si>
+  <si>
+    <t>.specialCourtesiesCode</t>
+  </si>
+  <si>
+    <t>PV1-16</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.specialArrangement</t>
+  </si>
+  <si>
+    <t>Wheelchair, translator, stretcher, etc.</t>
+  </si>
+  <si>
+    <t>Any special requests that have been made for this hospitalization encounter, such as the provision of specific equipment or other things.</t>
+  </si>
+  <si>
+    <t>Special arrangements.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
+  </si>
+  <si>
+    <t>.specialArrangementCode</t>
+  </si>
+  <si>
+    <t>PV1-15 / OBR-30 / OBR-43</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.destination</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Location|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
-    <t>The location/organization from which the patient came before admission</t>
-  </si>
-  <si>
-    <t>The location/organization from which the patient came before admission.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=ORG].role</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.admitSource</t>
-  </si>
-  <si>
-    <t>From where patient was admitted (physician referral, transfer)</t>
-  </si>
-  <si>
-    <t>From where patient was admitted (physician referral, transfer).</t>
-  </si>
-  <si>
-    <t>From where the patient was admitted.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
-  </si>
-  <si>
-    <t>.admissionReferralSourceCode</t>
-  </si>
-  <si>
-    <t>PV1-14</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.reAdmission</t>
-  </si>
-  <si>
-    <t>The type of hospital re-admission that has occurred (if any). If the value is absent, then this is not identified as a readmission</t>
-  </si>
-  <si>
-    <t>Whether this hospitalization is a readmission and why if known.</t>
-  </si>
-  <si>
-    <t>The reason for re-admission of this hospitalization encounter.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
-  </si>
-  <si>
-    <t>PV1-13</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dietPreference</t>
-  </si>
-  <si>
-    <t>Diet preferences reported by the patient</t>
-  </si>
-  <si>
-    <t>Diet preferences reported by the patient.</t>
-  </si>
-  <si>
-    <t>For example, a patient may request both a dairy-free and nut-free diet preference (not mutually exclusive).</t>
-  </si>
-  <si>
-    <t>Used to track patient's diet restrictions and/or preference. For a complete description of the nutrition needs of a patient during their stay, one should use the nutritionOrder resource which links to Encounter.</t>
-  </si>
-  <si>
-    <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
-  </si>
-  <si>
-    <t>PV1-38</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.specialCourtesy</t>
-  </si>
-  <si>
-    <t>Special courtesies (VIP, board member)</t>
-  </si>
-  <si>
-    <t>Special courtesies (VIP, board member).</t>
-  </si>
-  <si>
-    <t>Special courtesies.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
-  </si>
-  <si>
-    <t>.specialCourtesiesCode</t>
-  </si>
-  <si>
-    <t>PV1-16</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.specialArrangement</t>
-  </si>
-  <si>
-    <t>Wheelchair, translator, stretcher, etc.</t>
-  </si>
-  <si>
-    <t>Any special requests that have been made for this hospitalization encounter, such as the provision of specific equipment or other things.</t>
-  </si>
-  <si>
-    <t>Special arrangements.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
-  </si>
-  <si>
-    <t>.specialArrangementCode</t>
-  </si>
-  <si>
-    <t>PV1-15 / OBR-30 / OBR-43</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.destination</t>
-  </si>
-  <si>
     <t>Location/organization to which the patient is discharged</t>
   </si>
   <si>
@@ -1823,17 +1983,13 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
-</t>
-  </si>
-  <si>
     <t>The organization (facility) responsible for this encounter</t>
   </si>
   <si>
     <t>The organization that is primarily responsible for this Encounter's services. This MAY be the same as the organization on the Patient record, however it could be different, such as if the actor performing the services was from an external organization (which may be billed seperately) for an external consultation.  Refer to the example bundle showing an abbreviated set of Encounters for a colonoscopy.</t>
   </si>
   <si>
-    <t>EntiteJuridique</t>
+    <t>ESSMSAccueil</t>
   </si>
   <si>
     <t>.particiaption[typeCode=PFM].role</t>
@@ -2165,10 +2321,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO93"/>
+  <dimension ref="A1:AO109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.37890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.16015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.62109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2193,7 +2349,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="64.00390625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="62.0859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="78.5625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -5255,15 +5411,17 @@
         <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>90</v>
@@ -5272,23 +5430,21 @@
         <v>81</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5313,13 +5469,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5337,13 +5493,13 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>271</v>
+        <v>186</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
@@ -5352,27 +5508,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>277</v>
+        <v>191</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>192</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>193</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5383,7 +5539,7 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -5395,17 +5551,15 @@
         <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>282</v>
+        <v>201</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>283</v>
+        <v>202</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5454,19 +5608,19 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>204</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
@@ -5486,21 +5640,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>286</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
@@ -5512,15 +5666,17 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5557,31 +5713,31 @@
         <v>81</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>81</v>
@@ -5601,44 +5757,46 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>287</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5662,13 +5820,13 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>81</v>
+        <v>218</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>81</v>
+        <v>219</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5686,19 +5844,19 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
@@ -5707,56 +5865,56 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>288</v>
+        <v>224</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>225</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>290</v>
+        <v>226</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>291</v>
+        <v>227</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -5766,7 +5924,7 @@
         <v>81</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>81</v>
+        <v>279</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>81</v>
@@ -5781,13 +5939,11 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -5805,19 +5961,19 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
@@ -5826,21 +5982,21 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>81</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>293</v>
+        <v>235</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5860,19 +6016,23 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5881,10 +6041,10 @@
         <v>81</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>81</v>
+        <v>241</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>81</v>
@@ -5896,13 +6056,13 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
@@ -5920,10 +6080,10 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>293</v>
+        <v>242</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>90</v>
@@ -5941,21 +6101,21 @@
         <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>246</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5975,18 +6135,20 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>256</v>
+        <v>201</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>295</v>
+        <v>247</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5999,7 +6161,7 @@
         <v>81</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>81</v>
@@ -6035,10 +6197,10 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>251</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>90</v>
@@ -6056,21 +6218,21 @@
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>81</v>
+        <v>253</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>255</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6078,7 +6240,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
@@ -6093,13 +6255,13 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>298</v>
+        <v>256</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>257</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6126,13 +6288,13 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>303</v>
+        <v>81</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>81</v>
@@ -6150,10 +6312,10 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>90</v>
@@ -6171,21 +6333,21 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>306</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6196,7 +6358,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -6205,18 +6367,20 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6265,13 +6429,13 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>268</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
@@ -6286,21 +6450,21 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>205</v>
+        <v>269</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>81</v>
+        <v>270</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6308,7 +6472,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>90</v>
@@ -6317,21 +6481,23 @@
         <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>201</v>
+        <v>110</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>202</v>
+        <v>285</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6356,13 +6522,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>81</v>
+        <v>218</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -6380,10 +6546,10 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>204</v>
+        <v>284</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>90</v>
@@ -6392,34 +6558,34 @@
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>205</v>
+        <v>291</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>81</v>
+        <v>292</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6438,16 +6604,16 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>135</v>
+        <v>295</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>208</v>
+        <v>296</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>209</v>
+        <v>297</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>183</v>
+        <v>298</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6497,7 +6663,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>211</v>
+        <v>294</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6509,7 +6675,7 @@
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6529,46 +6695,42 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>290</v>
+        <v>202</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6616,19 +6778,19 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>292</v>
+        <v>204</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
@@ -6637,7 +6799,7 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6648,21 +6810,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6674,15 +6836,17 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>298</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>314</v>
+        <v>208</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6707,13 +6871,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>303</v>
+        <v>81</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6731,19 +6895,19 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>313</v>
+        <v>211</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6763,42 +6927,46 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>256</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6846,19 +7014,19 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
@@ -6867,7 +7035,7 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6878,10 +7046,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6889,10 +7057,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6901,20 +7069,18 @@
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6939,13 +7105,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>324</v>
+        <v>288</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>325</v>
+        <v>289</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6963,13 +7129,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -6981,24 +7147,24 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>327</v>
+        <v>205</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>328</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7006,7 +7172,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>90</v>
@@ -7018,16 +7184,16 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7054,13 +7220,13 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>332</v>
+        <v>81</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>333</v>
+        <v>81</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7078,10 +7244,10 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>90</v>
@@ -7096,7 +7262,7 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>205</v>
@@ -7105,15 +7271,15 @@
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7121,7 +7287,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
@@ -7133,16 +7299,16 @@
         <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7169,13 +7335,13 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -7193,10 +7359,10 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>90</v>
@@ -7214,32 +7380,32 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>341</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>343</v>
+        <v>81</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
@@ -7248,20 +7414,18 @@
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>344</v>
+        <v>295</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7310,13 +7474,13 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
@@ -7325,27 +7489,27 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>348</v>
+        <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>349</v>
+        <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>350</v>
+        <v>205</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>351</v>
+        <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>352</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7356,7 +7520,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7365,16 +7529,16 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>354</v>
+        <v>201</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>355</v>
+        <v>202</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>356</v>
+        <v>203</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7425,46 +7589,46 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>353</v>
+        <v>204</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>357</v>
+        <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>205</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>358</v>
+        <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>359</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>361</v>
+        <v>180</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7483,15 +7647,17 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>362</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>363</v>
+        <v>208</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7540,7 +7706,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>360</v>
+        <v>211</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7552,16 +7718,16 @@
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>365</v>
+        <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>366</v>
+        <v>205</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7572,14 +7738,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>367</v>
+        <v>325</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>367</v>
+        <v>325</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7592,22 +7758,26 @@
         <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>282</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>368</v>
+        <v>303</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7655,7 +7825,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>367</v>
+        <v>305</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7667,30 +7837,30 @@
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>370</v>
+        <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>371</v>
+        <v>133</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>326</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>326</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7698,7 +7868,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
@@ -7713,13 +7883,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>201</v>
+        <v>311</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>202</v>
+        <v>327</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>203</v>
+        <v>328</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7746,13 +7916,13 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>81</v>
+        <v>315</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7770,10 +7940,10 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>204</v>
+        <v>326</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>90</v>
@@ -7782,7 +7952,7 @@
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7802,21 +7972,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7828,17 +7998,15 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>256</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>208</v>
+        <v>330</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -7887,19 +8055,19 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>211</v>
+        <v>329</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -7919,14 +8087,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>375</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>375</v>
+        <v>332</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7939,26 +8107,24 @@
         <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>225</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>290</v>
+        <v>333</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>291</v>
+        <v>334</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7982,13 +8148,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>81</v>
+        <v>337</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>81</v>
+        <v>338</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -8006,7 +8172,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>292</v>
+        <v>332</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8018,30 +8184,30 @@
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>133</v>
+        <v>340</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>81</v>
+        <v>318</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8052,7 +8218,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -8067,14 +8233,12 @@
         <v>225</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8099,13 +8263,11 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>380</v>
+        <v>345</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8123,13 +8285,13 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
@@ -8138,27 +8300,27 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>81</v>
+        <v>346</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>381</v>
+        <v>339</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>382</v>
+        <v>205</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>383</v>
+        <v>347</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>384</v>
+        <v>348</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>384</v>
+        <v>348</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8181,13 +8343,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>385</v>
+        <v>349</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>386</v>
+        <v>350</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8214,13 +8376,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>81</v>
+        <v>350</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>81</v>
+        <v>351</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8238,7 +8400,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>384</v>
+        <v>348</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8259,29 +8421,29 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>387</v>
+        <v>352</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>81</v>
+        <v>353</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>388</v>
+        <v>354</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>81</v>
+        <v>356</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>90</v>
@@ -8296,15 +8458,17 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>390</v>
+        <v>357</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>391</v>
+        <v>358</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8353,7 +8517,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8368,27 +8532,27 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>81</v>
+        <v>361</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>393</v>
+        <v>362</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>396</v>
+        <v>365</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8411,13 +8575,13 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8468,7 +8632,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8486,35 +8650,35 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>401</v>
+        <v>205</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>81</v>
+        <v>371</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>402</v>
+        <v>372</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>81</v>
+        <v>374</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8526,17 +8690,15 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>256</v>
+        <v>375</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8585,13 +8747,13 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
@@ -8603,24 +8765,24 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>407</v>
+        <v>378</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>410</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8631,7 +8793,7 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8640,16 +8802,16 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>201</v>
+        <v>295</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>202</v>
+        <v>381</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>203</v>
+        <v>382</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8700,53 +8862,53 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>204</v>
+        <v>380</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>205</v>
+        <v>384</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>81</v>
+        <v>385</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -8758,17 +8920,15 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8805,31 +8965,31 @@
         <v>81</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>81</v>
@@ -8849,21 +9009,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>81</v>
@@ -8872,19 +9032,19 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>414</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>415</v>
+        <v>208</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>416</v>
+        <v>209</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>417</v>
+        <v>183</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8934,82 +9094,82 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>418</v>
+        <v>211</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>419</v>
+        <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>420</v>
+        <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>421</v>
+        <v>205</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>423</v>
+        <v>388</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>423</v>
+        <v>388</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>414</v>
+        <v>135</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>424</v>
+        <v>303</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>425</v>
+        <v>304</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q59" t="s" s="2">
-        <v>427</v>
-      </c>
+      <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9053,42 +9213,42 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>428</v>
+        <v>305</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>419</v>
+        <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>429</v>
+        <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>430</v>
+        <v>133</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>431</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9099,7 +9259,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>81</v>
@@ -9108,19 +9268,19 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>433</v>
+        <v>225</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>434</v>
+        <v>390</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>435</v>
+        <v>391</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>436</v>
+        <v>392</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9146,13 +9306,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9170,13 +9330,13 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
@@ -9188,35 +9348,35 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>437</v>
+        <v>395</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>438</v>
+        <v>396</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>439</v>
+        <v>397</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>439</v>
+        <v>397</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
@@ -9225,20 +9385,18 @@
         <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>441</v>
+        <v>398</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9263,13 +9421,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>445</v>
+        <v>81</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9287,13 +9445,13 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>439</v>
+        <v>397</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
@@ -9305,35 +9463,35 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>449</v>
+        <v>401</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>450</v>
+        <v>402</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>450</v>
+        <v>402</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9345,17 +9503,15 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>451</v>
+        <v>403</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>452</v>
+        <v>404</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9404,13 +9560,13 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>450</v>
+        <v>402</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
@@ -9422,24 +9578,24 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>446</v>
+        <v>406</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>447</v>
+        <v>407</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>448</v>
+        <v>408</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>449</v>
+        <v>409</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>453</v>
+        <v>410</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>453</v>
+        <v>410</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9450,7 +9606,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9459,16 +9615,16 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>282</v>
+        <v>201</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>454</v>
+        <v>202</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>455</v>
+        <v>203</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9519,19 +9675,19 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>453</v>
+        <v>204</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
@@ -9540,7 +9696,7 @@
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>456</v>
+        <v>205</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9551,21 +9707,21 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>457</v>
+        <v>411</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>457</v>
+        <v>411</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -9577,15 +9733,17 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9622,31 +9780,31 @@
         <v>81</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
@@ -9666,21 +9824,21 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>412</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>412</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -9689,19 +9847,19 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>208</v>
+        <v>413</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>209</v>
+        <v>414</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>183</v>
+        <v>415</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9751,19 +9909,19 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>211</v>
+        <v>416</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>81</v>
+        <v>417</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>81</v>
@@ -9772,7 +9930,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9783,46 +9941,44 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>290</v>
+        <v>419</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>291</v>
+        <v>420</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -9846,13 +10002,13 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -9870,19 +10026,19 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>292</v>
+        <v>424</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
@@ -9902,18 +10058,18 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>460</v>
+        <v>425</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>460</v>
+        <v>425</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>90</v>
@@ -9928,16 +10084,16 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>462</v>
+        <v>187</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>463</v>
+        <v>426</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>464</v>
+        <v>427</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9987,10 +10143,10 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>90</v>
@@ -10005,24 +10161,24 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>465</v>
+        <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>466</v>
+        <v>430</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>467</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>468</v>
+        <v>431</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>468</v>
+        <v>431</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10042,18 +10198,20 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>469</v>
+        <v>432</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -10078,13 +10236,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>471</v>
+        <v>81</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>472</v>
+        <v>81</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10102,7 +10260,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>468</v>
+        <v>435</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10117,13 +10275,13 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -10134,10 +10292,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10148,7 +10306,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -10157,16 +10315,16 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10217,13 +10375,13 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
@@ -10235,24 +10393,24 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>81</v>
+        <v>378</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>477</v>
+        <v>441</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10263,7 +10421,7 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>81</v>
@@ -10275,16 +10433,16 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>479</v>
+        <v>256</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>480</v>
+        <v>444</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>481</v>
+        <v>445</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>482</v>
+        <v>446</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10334,13 +10492,13 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>81</v>
@@ -10352,24 +10510,24 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>483</v>
+        <v>448</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10392,17 +10550,15 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>282</v>
+        <v>201</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>485</v>
+        <v>202</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -10451,7 +10607,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>484</v>
+        <v>204</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10463,7 +10619,7 @@
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
@@ -10472,7 +10628,7 @@
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>488</v>
+        <v>205</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10483,21 +10639,21 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>489</v>
+        <v>452</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>489</v>
+        <v>452</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>81</v>
@@ -10509,15 +10665,17 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10554,31 +10712,31 @@
         <v>81</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>81</v>
@@ -10598,21 +10756,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>490</v>
+        <v>453</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>490</v>
+        <v>453</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>81</v>
@@ -10621,19 +10779,19 @@
         <v>81</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>135</v>
+        <v>454</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>208</v>
+        <v>455</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>209</v>
+        <v>456</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>183</v>
+        <v>457</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10683,82 +10841,82 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>211</v>
+        <v>458</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>81</v>
+        <v>459</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>81</v>
+        <v>460</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>205</v>
+        <v>461</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>81</v>
+        <v>462</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>491</v>
+        <v>463</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>491</v>
+        <v>463</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>135</v>
+        <v>454</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>290</v>
+        <v>464</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>291</v>
+        <v>465</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q74" s="2"/>
+      <c r="Q74" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="R74" t="s" s="2">
         <v>81</v>
       </c>
@@ -10802,42 +10960,42 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>292</v>
+        <v>468</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>81</v>
+        <v>459</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>81</v>
+        <v>469</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>133</v>
+        <v>470</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>81</v>
+        <v>471</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10860,15 +11018,17 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>187</v>
+        <v>473</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -10917,7 +11077,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10935,35 +11095,35 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>192</v>
+        <v>477</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>495</v>
+        <v>478</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>81</v>
+        <v>480</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>81</v>
@@ -10972,18 +11132,20 @@
         <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>497</v>
+        <v>225</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -11008,13 +11170,13 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>81</v>
+        <v>484</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>81</v>
+        <v>485</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -11032,13 +11194,13 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>81</v>
@@ -11050,35 +11212,35 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>81</v>
+        <v>486</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>81</v>
+        <v>489</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>81</v>
+        <v>480</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>81</v>
@@ -11087,18 +11249,20 @@
         <v>81</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>225</v>
+        <v>491</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -11123,13 +11287,13 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>504</v>
+        <v>81</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>505</v>
+        <v>81</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -11147,13 +11311,13 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>81</v>
@@ -11165,24 +11329,24 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>81</v>
+        <v>486</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>507</v>
+        <v>489</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11193,7 +11357,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>81</v>
@@ -11202,16 +11366,16 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>225</v>
+        <v>295</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11238,13 +11402,13 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>511</v>
+        <v>81</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>512</v>
+        <v>81</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -11262,13 +11426,13 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>81</v>
@@ -11283,21 +11447,21 @@
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>205</v>
+        <v>496</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>513</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11308,7 +11472,7 @@
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>81</v>
@@ -11320,20 +11484,16 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>515</v>
+        <v>202</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>81</v>
       </c>
@@ -11357,13 +11517,13 @@
         <v>81</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>519</v>
+        <v>81</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>520</v>
+        <v>81</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>81</v>
@@ -11381,19 +11541,19 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>514</v>
+        <v>204</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>81</v>
@@ -11402,25 +11562,25 @@
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>521</v>
+        <v>205</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>522</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11439,15 +11599,17 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>524</v>
+        <v>208</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -11472,13 +11634,13 @@
         <v>81</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>526</v>
+        <v>81</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>527</v>
+        <v>81</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>81</v>
@@ -11496,7 +11658,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>523</v>
+        <v>211</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11508,7 +11670,7 @@
         <v>81</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>81</v>
@@ -11517,25 +11679,25 @@
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>528</v>
+        <v>205</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>529</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>530</v>
+        <v>499</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>530</v>
+        <v>499</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11548,22 +11710,26 @@
         <v>81</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>531</v>
+        <v>303</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>81</v>
       </c>
@@ -11587,13 +11753,13 @@
         <v>81</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>533</v>
+        <v>81</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>534</v>
+        <v>81</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>81</v>
@@ -11611,7 +11777,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>530</v>
+        <v>305</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11623,7 +11789,7 @@
         <v>81</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>81</v>
@@ -11632,29 +11798,29 @@
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>535</v>
+        <v>133</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>536</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>81</v>
+        <v>501</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>90</v>
@@ -11666,18 +11832,20 @@
         <v>81</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>538</v>
+        <v>503</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -11726,10 +11894,10 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>90</v>
@@ -11744,24 +11912,24 @@
         <v>81</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>540</v>
+        <v>506</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>541</v>
+        <v>507</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>542</v>
+        <v>508</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>542</v>
+        <v>508</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11787,10 +11955,10 @@
         <v>225</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>543</v>
+        <v>509</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>544</v>
+        <v>510</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11817,13 +11985,13 @@
         <v>81</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>323</v>
+        <v>114</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>545</v>
+        <v>511</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>546</v>
+        <v>512</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
@@ -11841,7 +12009,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>542</v>
+        <v>508</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11862,21 +12030,21 @@
         <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>547</v>
+        <v>205</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>548</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>549</v>
+        <v>513</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>549</v>
+        <v>513</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11887,7 +12055,7 @@
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>81</v>
@@ -11899,17 +12067,15 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>282</v>
+        <v>514</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>550</v>
+        <v>515</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -11958,13 +12124,13 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>549</v>
+        <v>513</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>81</v>
@@ -11979,7 +12145,7 @@
         <v>81</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>553</v>
+        <v>517</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
@@ -11990,10 +12156,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>554</v>
+        <v>518</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>554</v>
+        <v>518</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12004,7 +12170,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>81</v>
@@ -12016,15 +12182,17 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>201</v>
+        <v>519</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>202</v>
+        <v>520</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12073,19 +12241,19 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>204</v>
+        <v>518</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>81</v>
@@ -12094,7 +12262,7 @@
         <v>81</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>205</v>
+        <v>523</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>81</v>
@@ -12105,21 +12273,21 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>555</v>
+        <v>524</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>555</v>
+        <v>524</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>81</v>
@@ -12131,16 +12299,16 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>135</v>
+        <v>295</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>208</v>
+        <v>525</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>209</v>
+        <v>526</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>183</v>
+        <v>527</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12190,19 +12358,19 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>211</v>
+        <v>524</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>81</v>
@@ -12211,7 +12379,7 @@
         <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>205</v>
+        <v>528</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>81</v>
@@ -12222,46 +12390,42 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>556</v>
+        <v>529</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>556</v>
+        <v>529</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>290</v>
+        <v>202</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
       </c>
@@ -12309,19 +12473,19 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>292</v>
+        <v>204</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>81</v>
@@ -12330,7 +12494,7 @@
         <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -12341,10 +12505,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>557</v>
+        <v>530</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>557</v>
+        <v>530</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12352,10 +12516,10 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>81</v>
@@ -12367,13 +12531,13 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>558</v>
+        <v>135</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>559</v>
+        <v>136</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>560</v>
+        <v>137</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12412,56 +12576,56 @@
         <v>81</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC88" s="2"/>
       <c r="AD88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>557</v>
+        <v>211</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>561</v>
+        <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>394</v>
+        <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>562</v>
+        <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>563</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>564</v>
+        <v>531</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C89" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="D89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12482,17 +12646,15 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>110</v>
+        <v>533</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>565</v>
+        <v>534</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -12517,13 +12679,13 @@
         <v>81</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -12541,28 +12703,28 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>564</v>
+        <v>211</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>81</v>
+        <v>536</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -12573,44 +12735,46 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>571</v>
+        <v>537</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>571</v>
+        <v>537</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>572</v>
+        <v>303</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>573</v>
+        <v>304</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
       </c>
@@ -12634,13 +12798,13 @@
         <v>81</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>575</v>
+        <v>81</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>576</v>
+        <v>81</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -12658,19 +12822,19 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>571</v>
+        <v>305</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>81</v>
@@ -12679,7 +12843,7 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
@@ -12690,10 +12854,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12716,13 +12880,13 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>578</v>
+        <v>539</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>579</v>
+        <v>540</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12773,7 +12937,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12788,27 +12952,27 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>81</v>
+        <v>541</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>387</v>
+        <v>192</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>81</v>
+        <v>542</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>580</v>
+        <v>543</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>580</v>
+        <v>543</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12816,7 +12980,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>90</v>
@@ -12831,13 +12995,13 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>581</v>
+        <v>544</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>582</v>
+        <v>545</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>583</v>
+        <v>546</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12888,7 +13052,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>580</v>
+        <v>543</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12903,27 +13067,27 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>584</v>
+        <v>547</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>585</v>
+        <v>548</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>586</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>587</v>
+        <v>549</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>587</v>
+        <v>549</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12946,17 +13110,15 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>588</v>
+        <v>225</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>589</v>
+        <v>550</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>591</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -12981,13 +13143,13 @@
         <v>81</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>81</v>
+        <v>552</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>81</v>
+        <v>553</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>81</v>
@@ -13005,7 +13167,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>587</v>
+        <v>549</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13023,15 +13185,1873 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="AN93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO93" t="s" s="2">
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO109" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:06:51+00:00</t>
+    <t>2026-02-27T10:48:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:48:32+00:00</t>
+    <t>2026-02-27T17:34:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T17:34:14+00:00</t>
+    <t>2026-03-02T09:04:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T09:04:22+00:00</t>
+    <t>2026-03-02T10:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T10:45:03+00:00</t>
+    <t>2026-03-02T11:00:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T11:00:56+00:00</t>
+    <t>2026-03-16T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:16:38+00:00</t>
+    <t>2026-03-16T15:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:31:45+00:00</t>
+    <t>2026-03-17T17:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T17:41:27+00:00</t>
+    <t>2026-04-09T09:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4038" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4330" uniqueCount="667">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:33:58+00:00</t>
+    <t>2026-05-07T09:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -472,6 +472,10 @@
     <t>Cette extension implemente l'élément plannedStartDate de R5. elle permet l'ajout de la date d'entrée prévisionnelle dans le séjour</t>
   </si>
   <si>
+    <t>Element `Encounter.plannedStartDate` has a context of Encounter based on following the parent source element upwards and mapping to `Encounter`.
+Element `Encounter.plannedStartDate` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -479,6 +483,80 @@
     <t>dateEntreePrevisionnelle</t>
   </si>
   <si>
+    <t>Encounter.extension:TDDUI-plannedStartDate-r5.id</t>
+  </si>
+  <si>
+    <t>Encounter.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Encounter.extension:TDDUI-plannedStartDate-r5.extension</t>
+  </si>
+  <si>
+    <t>Encounter.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Encounter.extension:TDDUI-plannedStartDate-r5.url</t>
+  </si>
+  <si>
+    <t>Encounter.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/5.0/StructureDefinition/extension-Encounter.plannedStartDate</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Encounter.extension:TDDUI-plannedStartDate-r5.value[x]</t>
+  </si>
+  <si>
+    <t>Encounter.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>The planned start date/time (or admission date) of the encounter</t>
+  </si>
+  <si>
+    <t>The planned start date/time (or admission date) of the encounter.</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
     <t>Encounter.extension:TDDUI-plannedEndDate-r5</t>
   </si>
   <si>
@@ -495,7 +573,32 @@
     <t>Cette extension implemente l'élément plannedEndDate de R5. elle permet l'ajout de la date de sortie prévisionnelle du séjour</t>
   </si>
   <si>
+    <t>Element `Encounter.plannedEndDate` has a context of Encounter based on following the parent source element upwards and mapping to `Encounter`.
+Element `Encounter.plannedEndDate` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
+  </si>
+  <si>
     <t>dateSortiePrevisionnelle</t>
+  </si>
+  <si>
+    <t>Encounter.extension:TDDUI-plannedEndDate-r5.id</t>
+  </si>
+  <si>
+    <t>Encounter.extension:TDDUI-plannedEndDate-r5.extension</t>
+  </si>
+  <si>
+    <t>Encounter.extension:TDDUI-plannedEndDate-r5.url</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/5.0/StructureDefinition/extension-Encounter.plannedEndDate</t>
+  </si>
+  <si>
+    <t>Encounter.extension:TDDUI-plannedEndDate-r5.value[x]</t>
+  </si>
+  <si>
+    <t>The planned end date/time (or discharge date) of the encounter</t>
+  </si>
+  <si>
+    <t>The planned end date/time (or discharge date) of the encounter.</t>
   </si>
   <si>
     <t>Encounter.extension:TDDUIAdmissionDate</t>
@@ -648,22 +751,6 @@
     <t>Encounter.identifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Encounter.identifier:idStay.extension</t>
   </si>
   <si>
@@ -674,12 +761,6 @@
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Encounter.identifier:idStay.use</t>
@@ -1437,10 +1518,6 @@
   </si>
   <si>
     <t>Encounter.period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
   </si>
   <si>
     <t>Starting time with inclusive boundary</t>
@@ -2321,10 +2398,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO109"/>
+  <dimension ref="A1:AO117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.56640625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.16015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.62109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3457,7 +3534,9 @@
       <c r="M10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>81</v>
@@ -3515,19 +3594,19 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>81</v>
@@ -3538,14 +3617,12 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>81</v>
       </c>
@@ -3566,13 +3643,13 @@
         <v>81</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3623,28 +3700,28 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>81</v>
@@ -3655,14 +3732,12 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>81</v>
       </c>
@@ -3671,7 +3746,7 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>81</v>
@@ -3683,13 +3758,13 @@
         <v>81</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3728,19 +3803,19 @@
         <v>81</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3749,13 +3824,13 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>81</v>
@@ -3775,17 +3850,15 @@
         <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C13" t="s" s="2">
         <v>162</v>
       </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>90</v>
@@ -3800,22 +3873,24 @@
         <v>81</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>81</v>
@@ -3857,28 +3932,28 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>81</v>
@@ -3889,14 +3964,12 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>81</v>
       </c>
@@ -3917,13 +3990,13 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3974,28 +4047,28 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>81</v>
@@ -4006,13 +4079,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>81</v>
@@ -4034,15 +4107,17 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -4100,13 +4175,13 @@
         <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>141</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>81</v>
@@ -4123,46 +4198,42 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>81</v>
       </c>
@@ -4210,19 +4281,19 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>81</v>
@@ -4231,7 +4302,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -4242,10 +4313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4253,10 +4324,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -4265,16 +4336,16 @@
         <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>136</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>137</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4313,9 +4384,11 @@
         <v>81</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AC17" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="AD17" t="s" s="2">
         <v>81</v>
       </c>
@@ -4323,7 +4396,7 @@
         <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4335,34 +4408,32 @@
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>194</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>81</v>
       </c>
@@ -4380,25 +4451,27 @@
         <v>81</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>187</v>
+        <v>104</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>81</v>
@@ -4440,42 +4513,42 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>194</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4498,13 +4571,13 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4555,7 +4628,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4567,7 +4640,7 @@
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
@@ -4576,7 +4649,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -4587,21 +4660,23 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
@@ -4613,17 +4688,15 @@
         <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4660,19 +4733,19 @@
         <v>81</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>140</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4681,19 +4754,19 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>141</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -4704,12 +4777,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>81</v>
       </c>
@@ -4724,26 +4799,22 @@
         <v>81</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>81</v>
       </c>
@@ -4767,13 +4838,13 @@
         <v>81</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>219</v>
+        <v>81</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>81</v>
@@ -4791,50 +4862,52 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>140</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>222</v>
+        <v>81</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>90</v>
@@ -4846,23 +4919,19 @@
         <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>81</v>
       </c>
@@ -4871,7 +4940,7 @@
         <v>81</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>230</v>
+        <v>81</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>81</v>
@@ -4886,11 +4955,13 @@
         <v>81</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>231</v>
+        <v>81</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>81</v>
@@ -4908,50 +4979,52 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>140</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>222</v>
+        <v>81</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>233</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
@@ -4963,23 +5036,19 @@
         <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>104</v>
+        <v>208</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4988,10 +5057,10 @@
         <v>81</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="U23" t="s" s="2">
         <v>81</v>
@@ -5027,76 +5096,78 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>140</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>81</v>
+        <v>211</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>244</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
       </c>
@@ -5108,7 +5179,7 @@
         <v>81</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="U24" t="s" s="2">
         <v>81</v>
@@ -5144,19 +5215,19 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>81</v>
@@ -5165,21 +5236,21 @@
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>252</v>
+        <v>133</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>253</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5187,10 +5258,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
@@ -5202,13 +5273,13 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5247,25 +5318,23 @@
         <v>81</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>219</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
@@ -5277,32 +5346,34 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>81</v>
+        <v>226</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>261</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
@@ -5317,17 +5388,15 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5376,13 +5445,13 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>219</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
@@ -5391,31 +5460,29 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>81</v>
+        <v>226</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>270</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>81</v>
       </c>
@@ -5433,16 +5500,16 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>153</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5493,53 +5560,53 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>274</v>
+        <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>194</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -5551,15 +5618,17 @@
         <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5596,31 +5665,31 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
@@ -5629,7 +5698,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5640,44 +5709,46 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>238</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5701,43 +5772,43 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>81</v>
@@ -5746,21 +5817,21 @@
         <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5768,7 +5839,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>90</v>
@@ -5777,25 +5848,25 @@
         <v>81</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>110</v>
+        <v>251</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5805,7 +5876,7 @@
         <v>81</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>81</v>
+        <v>256</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>81</v>
@@ -5820,13 +5891,11 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5844,7 +5913,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5865,21 +5934,21 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>133</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5902,19 +5971,19 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>225</v>
+        <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -5924,10 +5993,10 @@
         <v>81</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>81</v>
@@ -5939,11 +6008,13 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>231</v>
+        <v>81</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -5961,7 +6032,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5982,21 +6053,21 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>233</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6019,20 +6090,18 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -6041,10 +6110,10 @@
         <v>81</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>81</v>
@@ -6080,7 +6149,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6101,21 +6170,21 @@
         <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>244</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6123,7 +6192,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>90</v>
@@ -6138,17 +6207,15 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>201</v>
+        <v>282</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -6161,7 +6228,7 @@
         <v>81</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>81</v>
@@ -6197,7 +6264,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6218,21 +6285,21 @@
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>253</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6255,15 +6322,17 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -6312,7 +6381,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>259</v>
+        <v>294</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6333,23 +6402,25 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>261</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6370,17 +6441,15 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6429,13 +6498,13 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>268</v>
+        <v>219</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
@@ -6444,27 +6513,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>81</v>
+        <v>226</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>270</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6472,7 +6541,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>90</v>
@@ -6481,23 +6550,21 @@
         <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>285</v>
+        <v>153</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6522,13 +6589,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -6546,10 +6613,10 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>284</v>
+        <v>155</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>90</v>
@@ -6558,34 +6625,34 @@
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>290</v>
+        <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>291</v>
+        <v>156</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>293</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>235</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6604,16 +6671,16 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>295</v>
+        <v>135</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>297</v>
+        <v>237</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>298</v>
+        <v>216</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6651,19 +6718,19 @@
         <v>81</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>294</v>
+        <v>160</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6675,7 +6742,7 @@
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6684,7 +6751,7 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6695,10 +6762,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>299</v>
+        <v>239</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6715,22 +6782,26 @@
         <v>81</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>201</v>
+        <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6754,13 +6825,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6778,7 +6849,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>204</v>
+        <v>247</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6790,7 +6861,7 @@
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
@@ -6799,32 +6870,32 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6833,21 +6904,23 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>135</v>
+        <v>251</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6856,7 +6929,7 @@
         <v>81</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>81</v>
@@ -6871,13 +6944,11 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6895,19 +6966,19 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>211</v>
+        <v>258</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6916,56 +6987,56 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>81</v>
+        <v>259</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>301</v>
+        <v>261</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>304</v>
+        <v>263</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>184</v>
+        <v>265</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6975,10 +7046,10 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>81</v>
@@ -7014,19 +7085,19 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>305</v>
+        <v>268</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
@@ -7035,21 +7106,21 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>133</v>
+        <v>269</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>81</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7069,18 +7140,20 @@
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -7093,7 +7166,7 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -7105,13 +7178,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -7129,10 +7202,10 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>306</v>
+        <v>277</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>90</v>
@@ -7150,21 +7223,21 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>205</v>
+        <v>278</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>81</v>
+        <v>279</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7172,7 +7245,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>90</v>
@@ -7184,16 +7257,16 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7244,10 +7317,10 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>90</v>
@@ -7265,21 +7338,21 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>205</v>
+        <v>286</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>81</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7287,7 +7360,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
@@ -7302,15 +7375,17 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7335,13 +7410,13 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>314</v>
+        <v>81</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>315</v>
+        <v>81</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>316</v>
+        <v>81</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -7359,10 +7434,10 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>90</v>
@@ -7380,21 +7455,21 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>318</v>
+        <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>319</v>
+        <v>296</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7402,30 +7477,32 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>295</v>
+        <v>110</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7450,13 +7527,13 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>81</v>
+        <v>315</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7474,13 +7551,13 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
@@ -7492,24 +7569,24 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>205</v>
+        <v>317</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>81</v>
+        <v>318</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>81</v>
+        <v>319</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7520,7 +7597,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7532,15 +7609,17 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>201</v>
+        <v>321</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>202</v>
+        <v>322</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7589,19 +7668,19 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>204</v>
+        <v>320</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
@@ -7610,7 +7689,7 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7621,21 +7700,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7647,17 +7726,15 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>208</v>
+        <v>153</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7706,19 +7783,19 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>211</v>
+        <v>155</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
@@ -7727,7 +7804,7 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7738,14 +7815,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>302</v>
+        <v>213</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7758,26 +7835,24 @@
         <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>303</v>
+        <v>236</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>304</v>
+        <v>237</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7825,7 +7900,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>305</v>
+        <v>160</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7846,7 +7921,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7857,42 +7932,46 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>81</v>
+        <v>328</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>311</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7916,13 +7995,13 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>314</v>
+        <v>81</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>315</v>
+        <v>81</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>316</v>
+        <v>81</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7940,19 +8019,19 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7961,7 +8040,7 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7972,10 +8051,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7998,13 +8077,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>256</v>
+        <v>110</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8031,13 +8110,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>81</v>
+        <v>315</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -8055,7 +8134,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -8076,7 +8155,7 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -8087,10 +8166,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8098,10 +8177,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -8110,20 +8189,18 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N50" t="s" s="2">
         <v>335</v>
       </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8148,13 +8225,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>337</v>
+        <v>81</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>338</v>
+        <v>81</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -8172,13 +8249,13 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
@@ -8190,24 +8267,24 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>340</v>
+        <v>156</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>318</v>
+        <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>341</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8215,7 +8292,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>90</v>
@@ -8230,13 +8307,13 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>225</v>
+        <v>337</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8263,11 +8340,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8285,10 +8364,10 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>90</v>
@@ -8300,27 +8379,27 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>205</v>
+        <v>343</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>81</v>
+        <v>344</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8331,7 +8410,7 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -8343,13 +8422,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>225</v>
+        <v>321</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8376,13 +8455,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>350</v>
+        <v>81</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>351</v>
+        <v>81</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8400,13 +8479,13 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
@@ -8421,29 +8500,29 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>352</v>
+        <v>156</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>353</v>
+        <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>354</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>356</v>
+        <v>81</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>90</v>
@@ -8455,20 +8534,18 @@
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>357</v>
+        <v>152</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>358</v>
+        <v>153</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8517,7 +8594,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>355</v>
+        <v>155</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8529,34 +8606,34 @@
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>361</v>
+        <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>362</v>
+        <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>363</v>
+        <v>156</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>364</v>
+        <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>365</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8572,18 +8649,20 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>367</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>368</v>
+        <v>236</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8632,7 +8711,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>366</v>
+        <v>160</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8644,34 +8723,34 @@
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>370</v>
+        <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>371</v>
+        <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>374</v>
+        <v>328</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8684,22 +8763,26 @@
         <v>81</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>375</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>376</v>
+        <v>329</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8747,7 +8830,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8759,16 +8842,16 @@
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>378</v>
+        <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>379</v>
+        <v>133</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -8779,10 +8862,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8790,10 +8873,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8802,16 +8885,16 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>295</v>
+        <v>337</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>381</v>
+        <v>353</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>382</v>
+        <v>354</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8838,13 +8921,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>81</v>
+        <v>342</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8862,13 +8945,13 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
@@ -8880,24 +8963,24 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>383</v>
+        <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>384</v>
+        <v>156</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>385</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8905,7 +8988,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>90</v>
@@ -8920,13 +9003,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>201</v>
+        <v>282</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>202</v>
+        <v>356</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>203</v>
+        <v>357</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8977,10 +9060,10 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>90</v>
@@ -8989,7 +9072,7 @@
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>81</v>
@@ -8998,7 +9081,7 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -9009,14 +9092,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>387</v>
+        <v>358</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>387</v>
+        <v>358</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9032,19 +9115,19 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>135</v>
+        <v>251</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>208</v>
+        <v>359</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>209</v>
+        <v>360</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>183</v>
+        <v>361</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9070,13 +9153,13 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>81</v>
+        <v>363</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>81</v>
+        <v>364</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -9094,7 +9177,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>211</v>
+        <v>358</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9106,66 +9189,62 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>205</v>
+        <v>366</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>81</v>
+        <v>344</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>81</v>
+        <v>367</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>135</v>
+        <v>251</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>303</v>
+        <v>369</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9189,13 +9268,11 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>81</v>
+        <v>371</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -9213,42 +9290,42 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>305</v>
+        <v>368</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>81</v>
+        <v>372</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>81</v>
+        <v>373</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9259,7 +9336,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>81</v>
@@ -9268,20 +9345,18 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9306,13 +9381,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9330,13 +9405,13 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
@@ -9348,32 +9423,32 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>394</v>
+        <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>81</v>
+        <v>379</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>396</v>
+        <v>380</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>81</v>
+        <v>382</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>90</v>
@@ -9385,18 +9460,20 @@
         <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>256</v>
+        <v>383</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9445,7 +9522,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9460,27 +9537,27 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>401</v>
+        <v>391</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9491,7 +9568,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9503,13 +9580,13 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9560,13 +9637,13 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
@@ -9578,35 +9655,35 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>407</v>
+        <v>156</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>409</v>
+        <v>398</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>81</v>
+        <v>400</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9618,13 +9695,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>202</v>
+        <v>402</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>203</v>
+        <v>403</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9675,28 +9752,28 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>204</v>
+        <v>399</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>81</v>
+        <v>404</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>205</v>
+        <v>405</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9707,14 +9784,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9730,20 +9807,18 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>321</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>208</v>
+        <v>407</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9780,19 +9855,19 @@
         <v>81</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>211</v>
+        <v>406</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9804,22 +9879,22 @@
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>205</v>
+        <v>410</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>81</v>
+        <v>411</v>
       </c>
     </row>
     <row r="65">
@@ -9847,20 +9922,18 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>413</v>
+        <v>153</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -9909,7 +9982,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>416</v>
+        <v>155</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9918,10 +9991,10 @@
         <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>417</v>
+        <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>81</v>
@@ -9930,7 +10003,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9941,21 +10014,21 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
@@ -9964,19 +10037,19 @@
         <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>419</v>
+        <v>236</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>420</v>
+        <v>237</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>421</v>
+        <v>216</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10002,13 +10075,13 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>314</v>
+        <v>81</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -10026,19 +10099,19 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>424</v>
+        <v>160</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
@@ -10047,7 +10120,7 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -10058,44 +10131,46 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>81</v>
+        <v>328</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>426</v>
+        <v>329</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>427</v>
+        <v>330</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
@@ -10143,19 +10218,19 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>429</v>
+        <v>331</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>81</v>
@@ -10164,7 +10239,7 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>430</v>
+        <v>133</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -10175,10 +10250,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10189,7 +10264,7 @@
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
@@ -10201,16 +10276,16 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10236,13 +10311,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>81</v>
+        <v>417</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>81</v>
+        <v>419</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10260,13 +10335,13 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>81</v>
@@ -10275,27 +10350,27 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>133</v>
+        <v>421</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10306,7 +10381,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -10315,16 +10390,16 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>438</v>
+        <v>282</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10375,13 +10450,13 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
@@ -10393,24 +10468,24 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>378</v>
+        <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>442</v>
+        <v>427</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10430,20 +10505,18 @@
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>256</v>
+        <v>429</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -10492,7 +10565,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10510,24 +10583,24 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>450</v>
+        <v>435</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10550,13 +10623,13 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>203</v>
+        <v>154</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10607,7 +10680,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10628,7 +10701,7 @@
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10639,14 +10712,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10668,13 +10741,13 @@
         <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10715,7 +10788,7 @@
         <v>138</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>81</v>
@@ -10724,7 +10797,7 @@
         <v>139</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10745,7 +10818,7 @@
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -10756,10 +10829,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10782,16 +10855,16 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>454</v>
+        <v>152</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10841,7 +10914,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10850,33 +10923,33 @@
         <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>460</v>
+        <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>461</v>
+        <v>133</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>462</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10899,24 +10972,22 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>454</v>
+        <v>104</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q74" t="s" s="2">
-        <v>467</v>
-      </c>
+      <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
         <v>81</v>
       </c>
@@ -10936,13 +11007,13 @@
         <v>81</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
@@ -10960,7 +11031,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10969,33 +11040,33 @@
         <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>459</v>
+        <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>469</v>
+        <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>470</v>
+        <v>133</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>471</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>472</v>
+        <v>451</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>472</v>
+        <v>451</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11015,19 +11086,19 @@
         <v>81</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>473</v>
+        <v>220</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>474</v>
+        <v>452</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>475</v>
+        <v>453</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11077,7 +11148,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11095,35 +11166,35 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>478</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>480</v>
+        <v>81</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>81</v>
@@ -11135,16 +11206,16 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11170,13 +11241,13 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>484</v>
+        <v>81</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>485</v>
+        <v>81</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -11194,13 +11265,13 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>81</v>
@@ -11209,31 +11280,31 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>81</v>
+        <v>462</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>487</v>
+        <v>133</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>488</v>
+        <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>489</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>480</v>
+        <v>81</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11252,17 +11323,15 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -11311,7 +11380,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11329,24 +11398,24 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>486</v>
+        <v>404</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>488</v>
+        <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>489</v>
+        <v>468</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>493</v>
+        <v>469</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>493</v>
+        <v>469</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11357,7 +11426,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>81</v>
@@ -11366,18 +11435,20 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>494</v>
+        <v>470</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -11426,13 +11497,13 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>493</v>
+        <v>469</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>81</v>
@@ -11444,24 +11515,24 @@
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>496</v>
+        <v>474</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>81</v>
+        <v>475</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>81</v>
+        <v>476</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>497</v>
+        <v>477</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>497</v>
+        <v>477</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11484,13 +11555,13 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>203</v>
+        <v>154</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11541,7 +11612,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11562,7 +11633,7 @@
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
@@ -11573,14 +11644,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11602,13 +11673,13 @@
         <v>135</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11646,19 +11717,19 @@
         <v>81</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11679,7 +11750,7 @@
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -11690,46 +11761,44 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J81" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>303</v>
+        <v>480</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>304</v>
+        <v>481</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>81</v>
       </c>
@@ -11777,50 +11846,50 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>305</v>
+        <v>483</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>81</v>
+        <v>484</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>81</v>
+        <v>485</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>133</v>
+        <v>486</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>81</v>
+        <v>487</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>501</v>
+        <v>81</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>90</v>
@@ -11835,22 +11904,24 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>502</v>
+        <v>170</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q82" s="2"/>
+      <c r="Q82" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="R82" t="s" s="2">
         <v>81</v>
       </c>
@@ -11894,42 +11965,42 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>81</v>
+        <v>484</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>81</v>
+        <v>494</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>505</v>
+        <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>488</v>
+        <v>81</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>507</v>
+        <v>496</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11952,15 +12023,17 @@
         <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>225</v>
+        <v>498</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>500</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>501</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -11985,13 +12058,13 @@
         <v>81</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>511</v>
+        <v>81</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>512</v>
+        <v>81</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
@@ -12009,7 +12082,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12027,35 +12100,35 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>205</v>
+        <v>502</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>81</v>
+        <v>503</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>81</v>
@@ -12064,18 +12137,20 @@
         <v>81</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>514</v>
+        <v>251</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -12100,13 +12175,13 @@
         <v>81</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>81</v>
+        <v>509</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>81</v>
+        <v>510</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -12124,13 +12199,13 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>81</v>
@@ -12142,28 +12217,28 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>81</v>
+        <v>511</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>81</v>
+        <v>513</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>81</v>
+        <v>514</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12179,19 +12254,19 @@
         <v>81</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12241,7 +12316,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12259,24 +12334,24 @@
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>81</v>
+        <v>511</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>81</v>
+        <v>513</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>81</v>
+        <v>514</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12287,7 +12362,7 @@
         <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>81</v>
@@ -12296,20 +12371,18 @@
         <v>81</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>81</v>
@@ -12358,13 +12431,13 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
@@ -12379,7 +12452,7 @@
         <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>81</v>
@@ -12390,10 +12463,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12416,13 +12489,13 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>203</v>
+        <v>154</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12473,7 +12546,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12494,7 +12567,7 @@
         <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -12505,14 +12578,14 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12534,12 +12607,14 @@
         <v>135</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>136</v>
+        <v>236</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>81</v>
@@ -12576,17 +12651,19 @@
         <v>81</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC88" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12607,7 +12684,7 @@
         <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
@@ -12618,44 +12695,46 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>81</v>
+        <v>328</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>533</v>
+        <v>135</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>534</v>
+        <v>329</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12703,7 +12782,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>211</v>
+        <v>331</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12712,19 +12791,19 @@
         <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>141</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>536</v>
+        <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -12735,46 +12814,44 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>302</v>
+        <v>526</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>135</v>
+        <v>527</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>303</v>
+        <v>528</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>304</v>
+        <v>529</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>81</v>
       </c>
@@ -12822,42 +12899,42 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>305</v>
+        <v>525</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>81</v>
+        <v>530</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>133</v>
+        <v>531</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>81</v>
+        <v>513</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12880,13 +12957,13 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>187</v>
+        <v>251</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12913,13 +12990,13 @@
         <v>81</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>81</v>
+        <v>536</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>81</v>
+        <v>537</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -12937,7 +13014,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12952,27 +13029,27 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>541</v>
+        <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>542</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12995,13 +13072,13 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13052,7 +13129,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13067,13 +13144,13 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>547</v>
+        <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
@@ -13084,10 +13161,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13098,7 +13175,7 @@
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>81</v>
@@ -13110,15 +13187,17 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>225</v>
+        <v>544</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>547</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -13143,13 +13222,13 @@
         <v>81</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>552</v>
+        <v>81</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>553</v>
+        <v>81</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>81</v>
@@ -13167,13 +13246,13 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>81</v>
@@ -13188,21 +13267,21 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>555</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13225,15 +13304,17 @@
         <v>81</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>225</v>
+        <v>321</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -13258,13 +13339,13 @@
         <v>81</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>559</v>
+        <v>81</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>560</v>
+        <v>81</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>81</v>
@@ -13282,7 +13363,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13303,21 +13384,21 @@
         <v>81</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>205</v>
+        <v>553</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>561</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13328,7 +13409,7 @@
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>81</v>
@@ -13340,20 +13421,16 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>563</v>
+        <v>153</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>566</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>81</v>
       </c>
@@ -13377,13 +13454,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -13401,19 +13478,19 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>562</v>
+        <v>155</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>81</v>
@@ -13422,21 +13499,21 @@
         <v>81</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>569</v>
+        <v>156</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13459,13 +13536,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>572</v>
+        <v>136</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>573</v>
+        <v>137</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13492,31 +13569,29 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>574</v>
+        <v>81</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>575</v>
+        <v>81</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC96" s="2"/>
       <c r="AD96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>571</v>
+        <v>160</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13528,7 +13603,7 @@
         <v>81</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>81</v>
@@ -13537,23 +13612,25 @@
         <v>81</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>576</v>
+        <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>577</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C97" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="D97" t="s" s="2">
         <v>81</v>
       </c>
@@ -13562,7 +13639,7 @@
         <v>79</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>81</v>
@@ -13574,13 +13651,13 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>225</v>
+        <v>558</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>579</v>
+        <v>559</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13607,13 +13684,13 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>581</v>
+        <v>81</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>582</v>
+        <v>81</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -13631,7 +13708,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>578</v>
+        <v>160</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13640,65 +13717,69 @@
         <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>81</v>
+        <v>561</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>583</v>
+        <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>584</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>585</v>
+        <v>562</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>585</v>
+        <v>562</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>81</v>
+        <v>328</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>586</v>
+        <v>135</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>587</v>
+        <v>329</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
       </c>
@@ -13746,19 +13827,19 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>585</v>
+        <v>331</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>81</v>
@@ -13767,21 +13848,21 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>589</v>
+        <v>133</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>590</v>
+        <v>81</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>591</v>
+        <v>563</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>591</v>
+        <v>563</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13804,13 +13885,13 @@
         <v>81</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>592</v>
+        <v>564</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>593</v>
+        <v>565</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13837,13 +13918,13 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>594</v>
+        <v>81</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>595</v>
+        <v>81</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
@@ -13861,7 +13942,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>591</v>
+        <v>563</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13876,27 +13957,27 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>81</v>
+        <v>566</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>596</v>
+        <v>225</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>597</v>
+        <v>567</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>598</v>
+        <v>568</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>598</v>
+        <v>568</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13907,7 +13988,7 @@
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>81</v>
@@ -13919,17 +14000,15 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>295</v>
+        <v>569</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>599</v>
+        <v>570</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -13978,13 +14057,13 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>598</v>
+        <v>568</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>81</v>
@@ -13993,13 +14072,13 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>81</v>
+        <v>572</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>602</v>
+        <v>573</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>81</v>
@@ -14010,10 +14089,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>603</v>
+        <v>574</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>603</v>
+        <v>574</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14036,13 +14115,13 @@
         <v>81</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>202</v>
+        <v>575</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>203</v>
+        <v>576</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14069,13 +14148,13 @@
         <v>81</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>81</v>
+        <v>577</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>81</v>
+        <v>578</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -14093,7 +14172,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>204</v>
+        <v>574</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14105,7 +14184,7 @@
         <v>81</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>81</v>
@@ -14114,32 +14193,32 @@
         <v>81</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>205</v>
+        <v>579</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>81</v>
+        <v>580</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>81</v>
@@ -14151,17 +14230,15 @@
         <v>81</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>135</v>
+        <v>251</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>208</v>
+        <v>582</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14186,13 +14263,13 @@
         <v>81</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>81</v>
+        <v>584</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>81</v>
+        <v>585</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -14210,19 +14287,19 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>211</v>
+        <v>581</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>81</v>
@@ -14231,25 +14308,25 @@
         <v>81</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>81</v>
+        <v>586</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14262,25 +14339,25 @@
         <v>81</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>135</v>
+        <v>251</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>303</v>
+        <v>588</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>304</v>
+        <v>589</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>183</v>
+        <v>590</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>184</v>
+        <v>591</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -14305,13 +14382,13 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>81</v>
+        <v>592</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>81</v>
+        <v>593</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -14329,7 +14406,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>305</v>
+        <v>587</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14341,7 +14418,7 @@
         <v>81</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>81</v>
@@ -14350,21 +14427,21 @@
         <v>81</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>133</v>
+        <v>594</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>81</v>
+        <v>595</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14372,10 +14449,10 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>81</v>
@@ -14387,13 +14464,13 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>607</v>
+        <v>251</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14420,13 +14497,13 @@
         <v>81</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>81</v>
+        <v>599</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>81</v>
+        <v>600</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
@@ -14444,13 +14521,13 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>81</v>
@@ -14462,24 +14539,24 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>610</v>
+        <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>407</v>
+        <v>601</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>611</v>
+        <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>612</v>
+        <v>602</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14490,7 +14567,7 @@
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>81</v>
@@ -14502,17 +14579,15 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>110</v>
+        <v>251</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -14537,13 +14612,13 @@
         <v>81</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>218</v>
+        <v>114</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>81</v>
@@ -14561,13 +14636,13 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>81</v>
@@ -14582,21 +14657,21 @@
         <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>81</v>
+        <v>609</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14619,17 +14694,15 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>225</v>
+        <v>611</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -14654,13 +14727,13 @@
         <v>81</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>624</v>
+        <v>81</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>625</v>
+        <v>81</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>81</v>
@@ -14678,7 +14751,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14699,21 +14772,21 @@
         <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>81</v>
+        <v>614</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>81</v>
+        <v>615</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14736,13 +14809,13 @@
         <v>81</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14769,13 +14842,13 @@
         <v>81</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>81</v>
+        <v>619</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>81</v>
+        <v>620</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
@@ -14793,7 +14866,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14814,21 +14887,21 @@
         <v>81</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>400</v>
+        <v>621</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>81</v>
+        <v>622</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14836,10 +14909,10 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>81</v>
@@ -14851,15 +14924,17 @@
         <v>81</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>544</v>
+        <v>321</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>625</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>81</v>
@@ -14908,13 +14983,13 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>81</v>
@@ -14923,27 +14998,27 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>632</v>
+        <v>81</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>634</v>
+        <v>81</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14966,17 +15041,15 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>636</v>
+        <v>152</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>637</v>
+        <v>153</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>639</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>81</v>
@@ -15025,33 +15098,965 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL112" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="AG109" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
+      <c r="AM112" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO109" t="s" s="2">
+      <c r="AK113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO117" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T09:37:23+00:00</t>
+    <t>2026-06-10T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T13:07:20+00:00</t>
+    <t>2026-06-16T08:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:06:32+00:00</t>
+    <t>2026-06-16T08:52:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:52:34+00:00</t>
+    <t>2026-06-16T09:33:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T09:33:33+00:00</t>
+    <t>2026-06-16T10:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:35:13+00:00</t>
+    <t>2026-06-16T10:46:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:46:14+00:00</t>
+    <t>2026-06-16T11:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T11:08:56+00:00</t>
+    <t>2026-06-16T14:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:39:41+00:00</t>
+    <t>2026-06-16T16:50:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:50:35+00:00</t>
+    <t>2026-06-17T09:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:02:27+00:00</t>
+    <t>2026-06-17T09:20:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:20:14+00:00</t>
+    <t>2026-06-29T13:11:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T13:11:00+00:00</t>
+    <t>2026-06-30T08:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:27:53+00:00</t>
+    <t>2026-06-30T13:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:41:45+00:00</t>
+    <t>2026-06-30T14:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:01:12+00:00</t>
+    <t>2026-06-30T14:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:55:37+00:00</t>
+    <t>2026-07-01T09:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T09:47:49+00:00</t>
+    <t>2026-07-01T11:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:47:31+00:00</t>
+    <t>2026-07-01T13:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:17:54+00:00</t>
+    <t>2026-07-01T14:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:33:44+00:00</t>
+    <t>2026-07-01T14:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:55:22+00:00</t>
+    <t>2026-07-01T15:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:33:30+00:00</t>
+    <t>2026-07-20T07:42:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.4.0-ballot</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T07:42:46+00:00</t>
+    <t>2026-07-22T13:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/main/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:04:03+00:00</t>
+    <t>2026-07-22T14:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
